--- a/data/raw/tbl_instrutores.xlsx
+++ b/data/raw/tbl_instrutores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Corporativo\COO\Operações\GPO - Planejamento\20. IA Projects\1 - SIPCAP - Sistema Integrado de Capacity Instrutores\SIPCAP\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://voeazul-my.sharepoint.com/personal/lucas_bezerra_voeazul_com_br/Documents/Área de Trabalho/SIPCAP/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E794179-3F9E-4C64-B73E-FE3F205893E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{5E794179-3F9E-4C64-B73E-FE3F205893E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B158337A-D7AB-4439-87A0-3C5DDD3C0064}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{0B145AC0-0935-4FA6-9AAD-18C1AE32E683}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$120</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="137">
   <si>
     <t>ALESSANDRO FIALHO BRONDANI</t>
   </si>
@@ -309,9 +309,6 @@
   </si>
   <si>
     <t>JORGE GERALDO SEABRA DE MELLO</t>
-  </si>
-  <si>
-    <t>GOAR ODYXE DUARTE NETO</t>
   </si>
   <si>
     <t>JOSE CARLOS SA DE CARVALHO FILHO</t>
@@ -1127,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E315442-6BD6-41B5-8D28-84728FE7DB6A}">
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" style="1" customWidth="1"/>
@@ -1144,34 +1141,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -1185,13 +1182,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -1209,13 +1206,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -1233,13 +1230,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1257,13 +1254,13 @@
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -1281,13 +1278,13 @@
         <v>7</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -1305,13 +1302,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1329,13 +1326,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1353,13 +1350,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1377,13 +1374,13 @@
         <v>7</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1401,13 +1398,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -1425,13 +1422,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -1449,13 +1446,13 @@
         <v>7</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -1473,13 +1470,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -1497,13 +1494,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -1521,13 +1518,13 @@
         <v>7</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -1545,13 +1542,13 @@
         <v>7</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1569,13 +1566,13 @@
         <v>7</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1593,13 +1590,13 @@
         <v>7</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1617,13 +1614,13 @@
         <v>7</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1641,13 +1638,13 @@
         <v>7</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1665,13 +1662,13 @@
         <v>7</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1689,13 +1686,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1713,13 +1710,13 @@
         <v>7</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -1737,13 +1734,13 @@
         <v>7</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -1761,13 +1758,13 @@
         <v>7</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -1785,13 +1782,13 @@
         <v>7</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -1809,13 +1806,13 @@
         <v>7</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -1833,13 +1830,13 @@
         <v>7</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -1857,13 +1854,13 @@
         <v>7</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1881,13 +1878,13 @@
         <v>7</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1905,13 +1902,13 @@
         <v>7</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1923,19 +1920,19 @@
         <v>22454</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -1947,19 +1944,19 @@
         <v>22457</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -1971,19 +1968,19 @@
         <v>22458</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1995,19 +1992,19 @@
         <v>22624</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -2019,19 +2016,19 @@
         <v>22859</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -2043,19 +2040,19 @@
         <v>22860</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -2067,19 +2064,19 @@
         <v>27175</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2091,19 +2088,19 @@
         <v>27176</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -2115,19 +2112,19 @@
         <v>27607</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -2139,19 +2136,19 @@
         <v>32910</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -2163,19 +2160,19 @@
         <v>32911</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -2187,19 +2184,19 @@
         <v>32912</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -2211,19 +2208,19 @@
         <v>32913</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -2235,19 +2232,19 @@
         <v>32974</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -2265,13 +2262,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -2289,13 +2286,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -2313,13 +2310,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -2337,13 +2334,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -2361,13 +2358,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -2385,13 +2382,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -2409,13 +2406,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -2433,13 +2430,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -2457,13 +2454,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -2481,13 +2478,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -2505,13 +2502,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -2529,13 +2526,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -2553,13 +2550,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -2577,13 +2574,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -2591,23 +2588,23 @@
       <c r="J60" s="4"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A61" s="14">
-        <v>21376</v>
+      <c r="A61" s="21">
+        <v>27609</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -2615,23 +2612,23 @@
       <c r="J61" s="4"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A62" s="21">
-        <v>27609</v>
+      <c r="A62" s="5">
+        <v>34256</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -2639,23 +2636,23 @@
       <c r="J62" s="4"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A63" s="5">
-        <v>34256</v>
+      <c r="A63" s="10">
+        <v>4153</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>3</v>
+        <v>41</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
@@ -2663,23 +2660,23 @@
       <c r="J63" s="4"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="10">
-        <v>4153</v>
+      <c r="A64" s="12">
+        <v>4542</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -2687,20 +2684,20 @@
       <c r="J64" s="4"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A65" s="12">
-        <v>4542</v>
+      <c r="A65" s="6">
+        <v>5197</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>129</v>
@@ -2711,23 +2708,23 @@
       <c r="J65" s="4"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" s="6">
-        <v>5197</v>
+      <c r="A66" s="25">
+        <v>6125</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -2735,23 +2732,23 @@
       <c r="J66" s="4"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A67" s="25">
-        <v>6125</v>
+      <c r="A67" s="26">
+        <v>8864</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -2759,23 +2756,23 @@
       <c r="J67" s="4"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="26">
-        <v>8864</v>
+      <c r="A68" s="27">
+        <v>11303</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
@@ -2783,23 +2780,23 @@
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" s="27">
-        <v>11303</v>
+      <c r="A69" s="22">
+        <v>15398</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -2807,23 +2804,23 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A70" s="22">
-        <v>15398</v>
+      <c r="A70" s="6">
+        <v>15418</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="11" t="s">
         <v>40</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -2831,23 +2828,23 @@
       <c r="J70" s="4"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="6">
-        <v>15418</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C71" s="11" t="s">
+      <c r="A71" s="21">
+        <v>15563</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -2855,23 +2852,23 @@
       <c r="J71" s="4"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" s="21">
-        <v>15563</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>78</v>
+      <c r="A72" s="22">
+        <v>15801</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -2879,20 +2876,20 @@
       <c r="J72" s="4"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="22">
-        <v>15801</v>
+      <c r="A73" s="12">
+        <v>19432</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>129</v>
@@ -2904,10 +2901,10 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
-        <v>19432</v>
+        <v>19765</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>40</v>
@@ -2915,11 +2912,11 @@
       <c r="D74" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
@@ -2928,22 +2925,22 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="12">
-        <v>19765</v>
+        <v>19877</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -2951,23 +2948,23 @@
       <c r="J75" s="4"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A76" s="12">
-        <v>19877</v>
+      <c r="A76" s="21">
+        <v>27177</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -2976,22 +2973,22 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="21">
-        <v>27177</v>
+        <v>30510</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -2999,23 +2996,23 @@
       <c r="J77" s="4"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A78" s="21">
-        <v>30510</v>
+      <c r="A78" s="5">
+        <v>34275</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -3024,22 +3021,22 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
-        <v>34275</v>
+        <v>34430</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -3047,20 +3044,20 @@
       <c r="J79" s="4"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A80" s="5">
-        <v>34430</v>
+      <c r="A80" s="14">
+        <v>182</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>129</v>
@@ -3071,11 +3068,11 @@
       <c r="J80" s="4"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A81" s="14">
-        <v>182</v>
+      <c r="A81" s="12">
+        <v>187</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>1</v>
@@ -3083,11 +3080,11 @@
       <c r="D81" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
@@ -3095,20 +3092,20 @@
       <c r="J81" s="4"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A82" s="12">
-        <v>187</v>
+      <c r="A82" s="5">
+        <v>1843</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>129</v>
@@ -3119,23 +3116,23 @@
       <c r="J82" s="4"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" s="5">
-        <v>1843</v>
+      <c r="A83" s="23">
+        <v>1853</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -3143,23 +3140,23 @@
       <c r="J83" s="4"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A84" s="23">
-        <v>1853</v>
+      <c r="A84" s="16">
+        <v>2075</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C84" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -3167,23 +3164,23 @@
       <c r="J84" s="4"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A85" s="16">
-        <v>2075</v>
+      <c r="A85" s="5">
+        <v>2167</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -3191,11 +3188,11 @@
       <c r="J85" s="4"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A86" s="5">
-        <v>2167</v>
+      <c r="A86" s="12">
+        <v>3178</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>1</v>
@@ -3204,10 +3201,10 @@
         <v>136</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
@@ -3215,23 +3212,23 @@
       <c r="J86" s="4"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A87" s="12">
-        <v>3178</v>
+      <c r="A87" s="9">
+        <v>3205</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E87" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E87" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
@@ -3239,20 +3236,20 @@
       <c r="J87" s="4"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A88" s="9">
-        <v>3205</v>
+      <c r="A88" s="14">
+        <v>3679</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>129</v>
@@ -3263,11 +3260,11 @@
       <c r="J88" s="4"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A89" s="14">
-        <v>3679</v>
+      <c r="A89" s="12">
+        <v>3853</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>1</v>
@@ -3276,10 +3273,10 @@
         <v>136</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -3287,23 +3284,23 @@
       <c r="J89" s="4"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A90" s="12">
-        <v>3853</v>
+      <c r="A90" s="9">
+        <v>3954</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E90" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -3311,23 +3308,23 @@
       <c r="J90" s="4"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A91" s="9">
-        <v>3954</v>
+      <c r="A91" s="21">
+        <v>5896</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
@@ -3335,20 +3332,20 @@
       <c r="J91" s="4"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A92" s="21">
-        <v>5896</v>
+      <c r="A92" s="17">
+        <v>5902</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>129</v>
@@ -3359,11 +3356,11 @@
       <c r="J92" s="4"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A93" s="17">
-        <v>5902</v>
+      <c r="A93" s="12">
+        <v>6220</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>1</v>
@@ -3371,11 +3368,11 @@
       <c r="D93" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E93" s="8" t="s">
+      <c r="E93" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -3383,20 +3380,20 @@
       <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A94" s="12">
-        <v>6220</v>
+      <c r="A94" s="14">
+        <v>7863</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>129</v>
@@ -3407,23 +3404,23 @@
       <c r="J94" s="4"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A95" s="14">
-        <v>7863</v>
+      <c r="A95" s="22">
+        <v>8220</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -3431,23 +3428,23 @@
       <c r="J95" s="4"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A96" s="22">
-        <v>8220</v>
+      <c r="A96" s="14">
+        <v>8451</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -3455,23 +3452,23 @@
       <c r="J96" s="4"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A97" s="14">
-        <v>8451</v>
+      <c r="A97" s="5">
+        <v>10034</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -3479,23 +3476,23 @@
       <c r="J97" s="4"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A98" s="5">
-        <v>10034</v>
+      <c r="A98" s="16">
+        <v>10255</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E98" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E98" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -3503,20 +3500,20 @@
       <c r="J98" s="4"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A99" s="16">
-        <v>10255</v>
+      <c r="A99" s="14">
+        <v>12451</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>129</v>
@@ -3528,22 +3525,22 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="14">
-        <v>12451</v>
+        <v>13105</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -3551,23 +3548,23 @@
       <c r="J100" s="4"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A101" s="14">
-        <v>13105</v>
+      <c r="A101" s="10">
+        <v>13543</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C101" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C101" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E101" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E101" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -3576,22 +3573,22 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="10">
-        <v>13543</v>
+        <v>15798</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -3599,23 +3596,23 @@
       <c r="J102" s="4"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A103" s="10">
-        <v>15798</v>
+      <c r="A103" s="5">
+        <v>19204</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C103" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -3624,22 +3621,22 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
-        <v>19204</v>
+        <v>19596</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -3648,22 +3645,22 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
-        <v>19596</v>
+        <v>19873</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
@@ -3671,20 +3668,20 @@
       <c r="J105" s="4"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A106" s="5">
-        <v>19873</v>
+      <c r="A106" s="22">
+        <v>22531</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C106" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C106" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>129</v>
@@ -3695,23 +3692,23 @@
       <c r="J106" s="4"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A107" s="22">
-        <v>22531</v>
+      <c r="A107" s="9">
+        <v>22612</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E107" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E107" s="6" t="s">
         <v>129</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
@@ -3719,11 +3716,11 @@
       <c r="J107" s="4"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A108" s="9">
-        <v>22612</v>
+      <c r="A108" s="28">
+        <v>25109</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>1</v>
@@ -3732,10 +3729,10 @@
         <v>136</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
@@ -3743,23 +3740,23 @@
       <c r="J108" s="4"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A109" s="28">
-        <v>25109</v>
+      <c r="A109" s="21">
+        <v>27523</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
@@ -3768,7 +3765,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="21">
-        <v>27523</v>
+        <v>27565</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>102</v>
@@ -3777,13 +3774,13 @@
         <v>1</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -3792,22 +3789,22 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="21">
-        <v>27565</v>
+        <v>30383</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
@@ -3816,22 +3813,22 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="21">
-        <v>30383</v>
+        <v>32752</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
@@ -3840,7 +3837,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="21">
-        <v>32752</v>
+        <v>32753</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>108</v>
@@ -3849,13 +3846,13 @@
         <v>1</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
@@ -3864,22 +3861,22 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="21">
-        <v>32753</v>
+        <v>32922</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
@@ -3887,23 +3884,23 @@
       <c r="J114" s="4"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A115" s="21">
-        <v>32922</v>
+      <c r="A115" s="5">
+        <v>34225</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -3912,22 +3909,22 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
-        <v>34225</v>
+        <v>34429</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
@@ -3936,22 +3933,22 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
-        <v>34429</v>
+        <v>39074</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -3959,23 +3956,23 @@
       <c r="J117" s="4"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A118" s="5">
-        <v>39074</v>
+      <c r="A118" s="23">
+        <v>39075</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C118" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C118" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -3983,23 +3980,23 @@
       <c r="J118" s="4"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A119" s="23">
-        <v>39075</v>
+      <c r="A119" s="5">
+        <v>39077</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C119" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -4007,20 +4004,20 @@
       <c r="J119" s="4"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A120" s="5">
-        <v>39077</v>
+      <c r="A120" s="20">
+        <v>11188</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>129</v>
@@ -4030,49 +4027,25 @@
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A121" s="20">
-        <v>11188</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H121" xr:uid="{4E315442-6BD6-41B5-8D28-84728FE7DB6A}"/>
-  <conditionalFormatting sqref="A1:A84">
-    <cfRule type="duplicateValues" dxfId="7" priority="60"/>
+  <autoFilter ref="A1:H120" xr:uid="{4E315442-6BD6-41B5-8D28-84728FE7DB6A}"/>
+  <conditionalFormatting sqref="A84:A85">
+    <cfRule type="duplicateValues" dxfId="7" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A120">
-    <cfRule type="duplicateValues" dxfId="6" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="63"/>
+  <conditionalFormatting sqref="A86:A119">
+    <cfRule type="duplicateValues" dxfId="6" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A85:A86">
-    <cfRule type="duplicateValues" dxfId="4" priority="45"/>
+  <conditionalFormatting sqref="A120">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A87:A120">
-    <cfRule type="duplicateValues" dxfId="3" priority="56"/>
+  <conditionalFormatting sqref="A1:A83">
+    <cfRule type="duplicateValues" dxfId="2" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A121">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="A1:A119">
+    <cfRule type="duplicateValues" dxfId="1" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
